--- a/Proposition-restructuration/ig/StructureDefinition-cds-entite-juridique.xlsx
+++ b/Proposition-restructuration/ig/StructureDefinition-cds-entite-juridique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:11:38+00:00</t>
+    <t>2026-07-16T08:39:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
